--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -41956,6 +41956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1809">
+      <c r="A1809" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1809" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1809" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1809" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1809" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -41979,6 +41979,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1810">
+      <c r="A1810" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1810" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1810" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1810" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1810" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42002,6 +42002,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1811">
+      <c r="A1811" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1811" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1811" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42025,6 +42025,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1812" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1812" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -41889,7 +41889,7 @@
     </row>
     <row r="1806">
       <c r="A1806" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1806" t="n">
         <v>0</v>
@@ -41912,7 +41912,7 @@
     </row>
     <row r="1807">
       <c r="A1807" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1807" t="n">
         <v>0</v>
@@ -41935,7 +41935,7 @@
     </row>
     <row r="1808">
       <c r="A1808" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1808" t="n">
         <v>0</v>
@@ -41958,7 +41958,7 @@
     </row>
     <row r="1809">
       <c r="A1809" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1809" t="n">
         <v>0</v>
@@ -41981,7 +41981,7 @@
     </row>
     <row r="1810">
       <c r="A1810" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1810" t="n">
         <v>0</v>
@@ -42004,7 +42004,7 @@
     </row>
     <row r="1811">
       <c r="A1811" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1811" t="n">
         <v>0</v>
@@ -42027,7 +42027,7 @@
     </row>
     <row r="1812">
       <c r="A1812" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1812" t="n">
         <v>0</v>
@@ -42045,6 +42045,29 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1812" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1813" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1813" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42071,6 +42071,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1814">
+      <c r="A1814" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1814" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1814" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1814" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1814" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1814" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1815" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1815" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42117,6 +42117,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1816" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1816" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42140,6 +42140,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42163,6 +42163,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1818" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1818" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1818" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42186,6 +42186,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1819" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1819" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1819" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42209,6 +42209,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1820" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1820" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1820" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1820" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42232,6 +42232,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1821" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1821" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42255,6 +42255,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1822" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1822" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42278,6 +42278,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1823" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1823" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1823" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1823" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42301,6 +42301,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1824" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1824" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1824" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1824" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42324,6 +42324,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1825" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1825" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1825" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1825" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1825" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42347,6 +42347,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1826" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1826" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1826" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1826" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42370,6 +42370,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1827" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1827" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42393,6 +42393,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1828" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42416,6 +42416,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1829" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42462,6 +42462,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1831">
+      <c r="A1831" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1831" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42485,6 +42485,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1832" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42508,6 +42508,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1833" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -42531,6 +42531,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1834" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53593,6 +53593,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1836">
+      <c r="A1836" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1836" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1836" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53622,6 +53622,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1837">
+      <c r="A1837" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1837" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1837" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53651,6 +53651,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1838">
+      <c r="A1838" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1838" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1838" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53680,6 +53680,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1839">
+      <c r="A1839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1839" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1839" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53709,6 +53709,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1840">
+      <c r="A1840" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1840" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1840" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53738,6 +53738,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1841">
+      <c r="A1841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1841" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1841" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53767,6 +53767,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1842" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1842" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53796,6 +53796,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1843">
+      <c r="A1843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1843" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1843" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TALEA.MI.xlsx
+++ b/data/TALEA.MI.xlsx
@@ -53825,6 +53825,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1844">
+      <c r="A1844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1844" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1844" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
